--- a/tests/data/duplicate-template.xlsx
+++ b/tests/data/duplicate-template.xlsx
@@ -453,7 +453,7 @@
         <v>Test</v>
       </c>
       <c r="C3" t="str">
-        <v>+919889169475</v>
+        <v>+919807102015</v>
       </c>
       <c r="D3" t="str">
         <v>India</v>
@@ -462,7 +462,7 @@
         <v>Emirates ID</v>
       </c>
       <c r="F3" t="str">
-        <v>784-1996-0343375-2</v>
+        <v>784-1980-4596975-7</v>
       </c>
       <c r="G3" t="str">
         <v>no</v>
